--- a/AI Audit Log_NguyenDucHuy.xlsx
+++ b/AI Audit Log_NguyenDucHuy.xlsx
@@ -4,13 +4,23 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9708" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 1 " sheetId="5" r:id="rId2"/>
+    <sheet name="Week 2" sheetId="2" r:id="rId3"/>
+    <sheet name="Week 3" sheetId="6" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="7" r:id="rId5"/>
+    <sheet name="Week 5" sheetId="8" r:id="rId6"/>
+    <sheet name="Week 6" sheetId="9" r:id="rId7"/>
+    <sheet name="Week 7" sheetId="10" r:id="rId8"/>
+    <sheet name="Week 8" sheetId="11" r:id="rId9"/>
+    <sheet name="Week 9" sheetId="12" r:id="rId10"/>
+    <sheet name="Week 10" sheetId="13" r:id="rId11"/>
+    <sheet name="Assignment 1" sheetId="14" r:id="rId12"/>
+    <sheet name="Assignment 2" sheetId="3" r:id="rId13"/>
+    <sheet name="Assignment 3" sheetId="4" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1264,7 +1274,7 @@
       </c>
       <c r="E1" s="9"/>
     </row>
-    <row r="2" ht="69" spans="1:5">
+    <row r="2" ht="41.4" spans="1:5">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -1278,7 +1288,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="55.2" spans="1:5">
+    <row r="3" ht="41.4" spans="1:5">
       <c r="A3" s="10">
         <v>2</v>
       </c>
@@ -1292,7 +1302,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="69" spans="1:5">
+    <row r="4" ht="41.4" spans="1:5">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -1306,7 +1316,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="82.8" spans="1:5">
+    <row r="5" ht="41.4" spans="1:5">
       <c r="A5" s="10">
         <v>4</v>
       </c>
@@ -1326,7 +1336,73 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F13"/>
@@ -1540,24 +1616,68 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>